--- a/input.xlsx
+++ b/input.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manos\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\prjectPlannerApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{132E168E-EC24-4EFB-851C-6A12A0BFC9C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1C207B8-9A82-4FB4-B2AB-FA09F3382C87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E25E9825-3837-433F-B906-F8A5D1A19F77}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="140">
   <si>
     <t xml:space="preserve">PI_ID </t>
   </si>
@@ -447,6 +447,15 @@
   </si>
   <si>
     <t>S38</t>
+  </si>
+  <si>
+    <t>F12</t>
+  </si>
+  <si>
+    <t>The CliniQ - History and Appointment Cared Redesign</t>
+  </si>
+  <si>
+    <t>PI2</t>
   </si>
 </sst>
 </file>
@@ -825,7 +834,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0C223FD-F271-4B4C-83E7-B00E61ACB151}">
-  <dimension ref="A1:U47"/>
+  <dimension ref="A1:U48"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.33203125" bestFit="1" customWidth="1"/>
@@ -2937,6 +2946,50 @@
         <v>46152</v>
       </c>
     </row>
+    <row r="48" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>139</v>
+      </c>
+      <c r="B48" t="s">
+        <v>100</v>
+      </c>
+      <c r="C48" t="s">
+        <v>109</v>
+      </c>
+      <c r="D48" t="s">
+        <v>88</v>
+      </c>
+      <c r="E48" t="s">
+        <v>137</v>
+      </c>
+      <c r="F48" t="s">
+        <v>24</v>
+      </c>
+      <c r="G48" t="s">
+        <v>136</v>
+      </c>
+      <c r="H48" t="s">
+        <v>138</v>
+      </c>
+      <c r="I48">
+        <v>2</v>
+      </c>
+      <c r="M48" t="s">
+        <v>41</v>
+      </c>
+      <c r="P48" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q48">
+        <v>10</v>
+      </c>
+      <c r="R48" s="1">
+        <v>46143</v>
+      </c>
+      <c r="S48" s="1">
+        <v>46152</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/input.xlsx
+++ b/input.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\prjectPlannerApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1C207B8-9A82-4FB4-B2AB-FA09F3382C87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{170D17D5-671A-440F-925C-FA7118ADA8E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E25E9825-3837-433F-B906-F8A5D1A19F77}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$U$51</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="150">
   <si>
     <t xml:space="preserve">PI_ID </t>
   </si>
@@ -371,9 +374,6 @@
     <t>Sprint 4</t>
   </si>
   <si>
-    <t>Analysis</t>
-  </si>
-  <si>
     <t>The CliniQ Web App</t>
   </si>
   <si>
@@ -456,6 +456,39 @@
   </si>
   <si>
     <t>PI2</t>
+  </si>
+  <si>
+    <t>Screen Flickring - Login screen</t>
+  </si>
+  <si>
+    <t>Booking UI design</t>
+  </si>
+  <si>
+    <t>Traffic log (Web/Mobile)</t>
+  </si>
+  <si>
+    <t>The CLiniQ (Web + Mobile)</t>
+  </si>
+  <si>
+    <t>F13</t>
+  </si>
+  <si>
+    <t>F14</t>
+  </si>
+  <si>
+    <t>F15</t>
+  </si>
+  <si>
+    <t>Converting Mobile APP to web App</t>
+  </si>
+  <si>
+    <t>S39</t>
+  </si>
+  <si>
+    <t>S40</t>
+  </si>
+  <si>
+    <t>S41</t>
   </si>
 </sst>
 </file>
@@ -834,13 +867,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0C223FD-F271-4B4C-83E7-B00E61ACB151}">
-  <dimension ref="A1:U48"/>
+  <dimension ref="A1:U51"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.21875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.77734375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8.109375" bestFit="1" customWidth="1"/>
@@ -2394,7 +2427,7 @@
         <v>106</v>
       </c>
       <c r="G35" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H35" t="s">
         <v>101</v>
@@ -2406,7 +2439,7 @@
         <v>41</v>
       </c>
       <c r="P35" t="s">
-        <v>99</v>
+        <v>42</v>
       </c>
       <c r="Q35">
         <v>10</v>
@@ -2438,7 +2471,7 @@
         <v>107</v>
       </c>
       <c r="G36" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H36" t="s">
         <v>102</v>
@@ -2450,7 +2483,7 @@
         <v>41</v>
       </c>
       <c r="P36" t="s">
-        <v>99</v>
+        <v>43</v>
       </c>
       <c r="Q36">
         <v>10</v>
@@ -2482,7 +2515,7 @@
         <v>107</v>
       </c>
       <c r="G37" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H37" t="s">
         <v>103</v>
@@ -2517,7 +2550,7 @@
         <v>109</v>
       </c>
       <c r="D38" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E38" t="s">
         <v>94</v>
@@ -2526,10 +2559,10 @@
         <v>46</v>
       </c>
       <c r="G38" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H38" t="s">
-        <v>111</v>
+        <v>146</v>
       </c>
       <c r="I38">
         <v>1</v>
@@ -2538,7 +2571,7 @@
         <v>41</v>
       </c>
       <c r="P38" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Q38">
         <v>10</v>
@@ -2570,7 +2603,7 @@
         <v>105</v>
       </c>
       <c r="G39" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H39" t="s">
         <v>104</v>
@@ -2614,10 +2647,10 @@
         <v>105</v>
       </c>
       <c r="G40" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I40">
         <v>5</v>
@@ -2658,10 +2691,10 @@
         <v>105</v>
       </c>
       <c r="G41" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H41" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I41">
         <v>5</v>
@@ -2702,19 +2735,19 @@
         <v>105</v>
       </c>
       <c r="G42" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H42" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I42">
         <v>5</v>
       </c>
       <c r="M42" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="P42" t="s">
-        <v>99</v>
+        <v>43</v>
       </c>
       <c r="Q42">
         <v>10</v>
@@ -2746,16 +2779,16 @@
         <v>105</v>
       </c>
       <c r="G43" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H43" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I43">
         <v>5</v>
       </c>
       <c r="M43" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="P43" t="s">
         <v>99</v>
@@ -2790,10 +2823,10 @@
         <v>105</v>
       </c>
       <c r="G44" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H44" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I44">
         <v>5</v>
@@ -2831,13 +2864,13 @@
         <v>96</v>
       </c>
       <c r="F45" t="s">
+        <v>112</v>
+      </c>
+      <c r="G45" t="s">
+        <v>133</v>
+      </c>
+      <c r="H45" t="s">
         <v>113</v>
-      </c>
-      <c r="G45" t="s">
-        <v>134</v>
-      </c>
-      <c r="H45" t="s">
-        <v>114</v>
       </c>
       <c r="I45">
         <v>2</v>
@@ -2875,19 +2908,19 @@
         <v>97</v>
       </c>
       <c r="F46" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G46" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H46" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I46">
         <v>5</v>
       </c>
       <c r="M46" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="P46" t="s">
         <v>99</v>
@@ -2919,19 +2952,19 @@
         <v>98</v>
       </c>
       <c r="F47" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G47" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H47" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I47">
         <v>5</v>
       </c>
       <c r="M47" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="P47" t="s">
         <v>99</v>
@@ -2948,7 +2981,7 @@
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B48" t="s">
         <v>100</v>
@@ -2960,16 +2993,16 @@
         <v>88</v>
       </c>
       <c r="E48" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F48" t="s">
         <v>24</v>
       </c>
       <c r="G48" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H48" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I48">
         <v>2</v>
@@ -2984,13 +3017,146 @@
         <v>10</v>
       </c>
       <c r="R48" s="1">
-        <v>46143</v>
+        <v>46133</v>
       </c>
       <c r="S48" s="1">
-        <v>46152</v>
+        <v>46142</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>138</v>
+      </c>
+      <c r="B49" t="s">
+        <v>100</v>
+      </c>
+      <c r="C49" t="s">
+        <v>109</v>
+      </c>
+      <c r="D49" t="s">
+        <v>111</v>
+      </c>
+      <c r="E49" t="s">
+        <v>143</v>
+      </c>
+      <c r="F49" t="s">
+        <v>24</v>
+      </c>
+      <c r="G49" t="s">
+        <v>147</v>
+      </c>
+      <c r="H49" t="s">
+        <v>139</v>
+      </c>
+      <c r="I49">
+        <v>2</v>
+      </c>
+      <c r="M49" t="s">
+        <v>41</v>
+      </c>
+      <c r="P49" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q49">
+        <v>10</v>
+      </c>
+      <c r="R49" s="1">
+        <v>46133</v>
+      </c>
+      <c r="S49" s="1">
+        <v>46142</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>138</v>
+      </c>
+      <c r="B50" t="s">
+        <v>100</v>
+      </c>
+      <c r="C50" t="s">
+        <v>109</v>
+      </c>
+      <c r="D50" t="s">
+        <v>111</v>
+      </c>
+      <c r="E50" t="s">
+        <v>144</v>
+      </c>
+      <c r="F50" t="s">
+        <v>24</v>
+      </c>
+      <c r="G50" t="s">
+        <v>148</v>
+      </c>
+      <c r="H50" t="s">
+        <v>140</v>
+      </c>
+      <c r="I50">
+        <v>2</v>
+      </c>
+      <c r="M50" t="s">
+        <v>41</v>
+      </c>
+      <c r="P50" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q50">
+        <v>10</v>
+      </c>
+      <c r="R50" s="1">
+        <v>46133</v>
+      </c>
+      <c r="S50" s="1">
+        <v>46142</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>138</v>
+      </c>
+      <c r="B51" t="s">
+        <v>100</v>
+      </c>
+      <c r="C51" t="s">
+        <v>109</v>
+      </c>
+      <c r="D51" t="s">
+        <v>142</v>
+      </c>
+      <c r="E51" t="s">
+        <v>145</v>
+      </c>
+      <c r="F51" t="s">
+        <v>106</v>
+      </c>
+      <c r="G51" t="s">
+        <v>149</v>
+      </c>
+      <c r="H51" t="s">
+        <v>141</v>
+      </c>
+      <c r="I51">
+        <v>2</v>
+      </c>
+      <c r="M51" t="s">
+        <v>41</v>
+      </c>
+      <c r="P51" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q51">
+        <v>10</v>
+      </c>
+      <c r="R51" s="1">
+        <v>46133</v>
+      </c>
+      <c r="S51" s="1">
+        <v>46142</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:U51" xr:uid="{A0C223FD-F271-4B4C-83E7-B00E61ACB151}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/input.xlsx
+++ b/input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\prjectPlannerApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{170D17D5-671A-440F-925C-FA7118ADA8E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EDC4AB4-C2CD-41F9-9126-39E9C1636D62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E25E9825-3837-433F-B906-F8A5D1A19F77}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="155">
   <si>
     <t xml:space="preserve">PI_ID </t>
   </si>
@@ -489,6 +489,21 @@
   </si>
   <si>
     <t>S41</t>
+  </si>
+  <si>
+    <t>F16</t>
+  </si>
+  <si>
+    <t>Doctor Mobile App</t>
+  </si>
+  <si>
+    <t>S42</t>
+  </si>
+  <si>
+    <t>Prescription Functionality as Web App</t>
+  </si>
+  <si>
+    <t>Auto Suggestion of medicine and Test List, Medicine Time and Frequency</t>
   </si>
 </sst>
 </file>
@@ -867,7 +882,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0C223FD-F271-4B4C-83E7-B00E61ACB151}">
-  <dimension ref="A1:U51"/>
+  <dimension ref="A1:U52"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.33203125" bestFit="1" customWidth="1"/>
@@ -881,7 +896,7 @@
     <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7.77734375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="35.88671875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="10.6640625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="10.21875" bestFit="1" customWidth="1"/>
@@ -3155,6 +3170,53 @@
         <v>46142</v>
       </c>
     </row>
+    <row r="52" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>138</v>
+      </c>
+      <c r="B52" t="s">
+        <v>100</v>
+      </c>
+      <c r="C52" t="s">
+        <v>109</v>
+      </c>
+      <c r="D52" t="s">
+        <v>151</v>
+      </c>
+      <c r="E52" t="s">
+        <v>150</v>
+      </c>
+      <c r="F52" t="s">
+        <v>24</v>
+      </c>
+      <c r="G52" t="s">
+        <v>152</v>
+      </c>
+      <c r="H52" t="s">
+        <v>153</v>
+      </c>
+      <c r="I52">
+        <v>2</v>
+      </c>
+      <c r="L52" t="s">
+        <v>154</v>
+      </c>
+      <c r="M52" t="s">
+        <v>41</v>
+      </c>
+      <c r="P52" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q52">
+        <v>10</v>
+      </c>
+      <c r="R52" s="1">
+        <v>46133</v>
+      </c>
+      <c r="S52" s="1">
+        <v>46142</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:U51" xr:uid="{A0C223FD-F271-4B4C-83E7-B00E61ACB151}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/input.xlsx
+++ b/input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\prjectPlannerApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EDC4AB4-C2CD-41F9-9126-39E9C1636D62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9EADF62-4A53-467C-B180-4CBEA02C3C1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E25E9825-3837-433F-B906-F8A5D1A19F77}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$U$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$U$50</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="155">
   <si>
     <t xml:space="preserve">PI_ID </t>
   </si>
@@ -882,7 +882,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0C223FD-F271-4B4C-83E7-B00E61ACB151}">
-  <dimension ref="A1:U52"/>
+  <dimension ref="A1:U51"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.33203125" bestFit="1" customWidth="1"/>
@@ -1917,7 +1917,7 @@
         <v>74</v>
       </c>
       <c r="H23" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I23">
         <v>2</v>
@@ -1926,7 +1926,7 @@
         <v>41</v>
       </c>
       <c r="P23" t="s">
-        <v>99</v>
+        <v>42</v>
       </c>
       <c r="Q23">
         <v>10</v>
@@ -1949,10 +1949,10 @@
         <v>108</v>
       </c>
       <c r="D24" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E24" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F24" t="s">
         <v>46</v>
@@ -1961,7 +1961,7 @@
         <v>75</v>
       </c>
       <c r="H24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I24">
         <v>2</v>
@@ -2005,7 +2005,7 @@
         <v>76</v>
       </c>
       <c r="H25" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="I25">
         <v>2</v>
@@ -2014,7 +2014,7 @@
         <v>41</v>
       </c>
       <c r="P25" t="s">
-        <v>42</v>
+        <v>99</v>
       </c>
       <c r="Q25">
         <v>10</v>
@@ -2049,7 +2049,7 @@
         <v>77</v>
       </c>
       <c r="H26" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="I26">
         <v>2</v>
@@ -2058,7 +2058,7 @@
         <v>41</v>
       </c>
       <c r="P26" t="s">
-        <v>99</v>
+        <v>42</v>
       </c>
       <c r="Q26">
         <v>10</v>
@@ -2093,7 +2093,7 @@
         <v>78</v>
       </c>
       <c r="H27" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I27">
         <v>2</v>
@@ -2137,7 +2137,7 @@
         <v>79</v>
       </c>
       <c r="H28" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I28">
         <v>2</v>
@@ -2181,7 +2181,7 @@
         <v>80</v>
       </c>
       <c r="H29" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I29">
         <v>2</v>
@@ -2225,7 +2225,7 @@
         <v>81</v>
       </c>
       <c r="H30" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I30">
         <v>2</v>
@@ -2269,7 +2269,7 @@
         <v>82</v>
       </c>
       <c r="H31" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I31">
         <v>2</v>
@@ -2313,7 +2313,7 @@
         <v>83</v>
       </c>
       <c r="H32" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I32">
         <v>2</v>
@@ -2357,7 +2357,7 @@
         <v>84</v>
       </c>
       <c r="H33" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I33">
         <v>2</v>
@@ -2386,25 +2386,25 @@
         <v>100</v>
       </c>
       <c r="C34" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D34" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E34" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F34" t="s">
-        <v>46</v>
+        <v>106</v>
       </c>
       <c r="G34" t="s">
         <v>85</v>
       </c>
       <c r="H34" t="s">
-        <v>65</v>
+        <v>101</v>
       </c>
       <c r="I34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M34" t="s">
         <v>41</v>
@@ -2416,10 +2416,10 @@
         <v>10</v>
       </c>
       <c r="R34" s="1">
-        <v>46123</v>
+        <v>46133</v>
       </c>
       <c r="S34" s="1">
-        <v>46132</v>
+        <v>46142</v>
       </c>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.3">
@@ -2436,25 +2436,25 @@
         <v>88</v>
       </c>
       <c r="E35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F35" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G35" t="s">
         <v>121</v>
       </c>
       <c r="H35" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I35">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M35" t="s">
         <v>41</v>
       </c>
       <c r="P35" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q35">
         <v>10</v>
@@ -2480,7 +2480,7 @@
         <v>88</v>
       </c>
       <c r="E36" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F36" t="s">
         <v>107</v>
@@ -2489,7 +2489,7 @@
         <v>122</v>
       </c>
       <c r="H36" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I36">
         <v>3</v>
@@ -2498,7 +2498,7 @@
         <v>41</v>
       </c>
       <c r="P36" t="s">
-        <v>43</v>
+        <v>99</v>
       </c>
       <c r="Q36">
         <v>10</v>
@@ -2521,28 +2521,28 @@
         <v>109</v>
       </c>
       <c r="D37" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="E37" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F37" t="s">
-        <v>107</v>
+        <v>46</v>
       </c>
       <c r="G37" t="s">
         <v>123</v>
       </c>
       <c r="H37" t="s">
-        <v>103</v>
+        <v>146</v>
       </c>
       <c r="I37">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M37" t="s">
         <v>41</v>
       </c>
       <c r="P37" t="s">
-        <v>99</v>
+        <v>42</v>
       </c>
       <c r="Q37">
         <v>10</v>
@@ -2565,28 +2565,28 @@
         <v>109</v>
       </c>
       <c r="D38" t="s">
-        <v>111</v>
+        <v>88</v>
       </c>
       <c r="E38" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F38" t="s">
-        <v>46</v>
+        <v>105</v>
       </c>
       <c r="G38" t="s">
         <v>124</v>
       </c>
       <c r="H38" t="s">
-        <v>146</v>
+        <v>104</v>
       </c>
       <c r="I38">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M38" t="s">
         <v>41</v>
       </c>
       <c r="P38" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q38">
         <v>10</v>
@@ -2612,7 +2612,7 @@
         <v>88</v>
       </c>
       <c r="E39" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F39" t="s">
         <v>105</v>
@@ -2621,16 +2621,16 @@
         <v>125</v>
       </c>
       <c r="H39" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="I39">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M39" t="s">
         <v>41</v>
       </c>
       <c r="P39" t="s">
-        <v>43</v>
+        <v>99</v>
       </c>
       <c r="Q39">
         <v>10</v>
@@ -2665,7 +2665,7 @@
         <v>126</v>
       </c>
       <c r="H40" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I40">
         <v>5</v>
@@ -2709,16 +2709,16 @@
         <v>127</v>
       </c>
       <c r="H41" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I41">
         <v>5</v>
       </c>
       <c r="M41" t="s">
-        <v>41</v>
+        <v>114</v>
       </c>
       <c r="P41" t="s">
-        <v>99</v>
+        <v>43</v>
       </c>
       <c r="Q41">
         <v>10</v>
@@ -2753,16 +2753,16 @@
         <v>128</v>
       </c>
       <c r="H42" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I42">
         <v>5</v>
       </c>
       <c r="M42" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="P42" t="s">
-        <v>43</v>
+        <v>99</v>
       </c>
       <c r="Q42">
         <v>10</v>
@@ -2797,13 +2797,13 @@
         <v>129</v>
       </c>
       <c r="H43" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I43">
         <v>5</v>
       </c>
       <c r="M43" t="s">
-        <v>119</v>
+        <v>41</v>
       </c>
       <c r="P43" t="s">
         <v>99</v>
@@ -2835,16 +2835,16 @@
         <v>96</v>
       </c>
       <c r="F44" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="G44" t="s">
         <v>130</v>
       </c>
       <c r="H44" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="I44">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M44" t="s">
         <v>41</v>
@@ -2876,7 +2876,7 @@
         <v>88</v>
       </c>
       <c r="E45" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F45" t="s">
         <v>112</v>
@@ -2885,13 +2885,13 @@
         <v>133</v>
       </c>
       <c r="H45" t="s">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="I45">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M45" t="s">
-        <v>41</v>
+        <v>114</v>
       </c>
       <c r="P45" t="s">
         <v>99</v>
@@ -2914,13 +2914,13 @@
         <v>100</v>
       </c>
       <c r="C46" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D46" t="s">
         <v>88</v>
       </c>
       <c r="E46" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F46" t="s">
         <v>112</v>
@@ -2935,7 +2935,7 @@
         <v>5</v>
       </c>
       <c r="M46" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="P46" t="s">
         <v>99</v>
@@ -2944,42 +2944,42 @@
         <v>10</v>
       </c>
       <c r="R46" s="1">
-        <v>46133</v>
+        <v>46143</v>
       </c>
       <c r="S46" s="1">
-        <v>46142</v>
+        <v>46152</v>
       </c>
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>16</v>
+        <v>138</v>
       </c>
       <c r="B47" t="s">
         <v>100</v>
       </c>
       <c r="C47" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D47" t="s">
         <v>88</v>
       </c>
       <c r="E47" t="s">
-        <v>98</v>
+        <v>136</v>
       </c>
       <c r="F47" t="s">
-        <v>112</v>
+        <v>24</v>
       </c>
       <c r="G47" t="s">
         <v>135</v>
       </c>
       <c r="H47" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="I47">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M47" t="s">
-        <v>132</v>
+        <v>41</v>
       </c>
       <c r="P47" t="s">
         <v>99</v>
@@ -2988,10 +2988,10 @@
         <v>10</v>
       </c>
       <c r="R47" s="1">
-        <v>46143</v>
+        <v>46133</v>
       </c>
       <c r="S47" s="1">
-        <v>46152</v>
+        <v>46142</v>
       </c>
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.3">
@@ -3005,19 +3005,19 @@
         <v>109</v>
       </c>
       <c r="D48" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="E48" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="F48" t="s">
         <v>24</v>
       </c>
       <c r="G48" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="H48" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I48">
         <v>2</v>
@@ -3052,16 +3052,16 @@
         <v>111</v>
       </c>
       <c r="E49" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F49" t="s">
         <v>24</v>
       </c>
       <c r="G49" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H49" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I49">
         <v>2</v>
@@ -3093,19 +3093,19 @@
         <v>109</v>
       </c>
       <c r="D50" t="s">
-        <v>111</v>
+        <v>142</v>
       </c>
       <c r="E50" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F50" t="s">
-        <v>24</v>
+        <v>106</v>
       </c>
       <c r="G50" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H50" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I50">
         <v>2</v>
@@ -3137,22 +3137,25 @@
         <v>109</v>
       </c>
       <c r="D51" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="E51" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="F51" t="s">
-        <v>106</v>
+        <v>24</v>
       </c>
       <c r="G51" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="H51" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="I51">
         <v>2</v>
+      </c>
+      <c r="L51" t="s">
+        <v>154</v>
       </c>
       <c r="M51" t="s">
         <v>41</v>
@@ -3170,55 +3173,8 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
-        <v>138</v>
-      </c>
-      <c r="B52" t="s">
-        <v>100</v>
-      </c>
-      <c r="C52" t="s">
-        <v>109</v>
-      </c>
-      <c r="D52" t="s">
-        <v>151</v>
-      </c>
-      <c r="E52" t="s">
-        <v>150</v>
-      </c>
-      <c r="F52" t="s">
-        <v>24</v>
-      </c>
-      <c r="G52" t="s">
-        <v>152</v>
-      </c>
-      <c r="H52" t="s">
-        <v>153</v>
-      </c>
-      <c r="I52">
-        <v>2</v>
-      </c>
-      <c r="L52" t="s">
-        <v>154</v>
-      </c>
-      <c r="M52" t="s">
-        <v>41</v>
-      </c>
-      <c r="P52" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q52">
-        <v>10</v>
-      </c>
-      <c r="R52" s="1">
-        <v>46133</v>
-      </c>
-      <c r="S52" s="1">
-        <v>46142</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:U51" xr:uid="{A0C223FD-F271-4B4C-83E7-B00E61ACB151}"/>
+  <autoFilter ref="A1:U50" xr:uid="{A0C223FD-F271-4B4C-83E7-B00E61ACB151}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/input.xlsx
+++ b/input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\prjectPlannerApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9EADF62-4A53-467C-B180-4CBEA02C3C1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{727A093E-6D93-4EE2-8C7A-29C3F8B1ACE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E25E9825-3837-433F-B906-F8A5D1A19F77}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="160">
   <si>
     <t xml:space="preserve">PI_ID </t>
   </si>
@@ -504,6 +504,21 @@
   </si>
   <si>
     <t>Auto Suggestion of medicine and Test List, Medicine Time and Frequency</t>
+  </si>
+  <si>
+    <t>Refund Initiate by Admin</t>
+  </si>
+  <si>
+    <t>Admin (Web + Mobile)</t>
+  </si>
+  <si>
+    <t>F17</t>
+  </si>
+  <si>
+    <t>Booking</t>
+  </si>
+  <si>
+    <t>S43</t>
   </si>
 </sst>
 </file>
@@ -882,7 +897,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0C223FD-F271-4B4C-83E7-B00E61ACB151}">
-  <dimension ref="A1:U51"/>
+  <dimension ref="A1:U52"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.33203125" bestFit="1" customWidth="1"/>
@@ -3173,6 +3188,50 @@
         <v>46142</v>
       </c>
     </row>
+    <row r="52" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>138</v>
+      </c>
+      <c r="B52" t="s">
+        <v>100</v>
+      </c>
+      <c r="C52" t="s">
+        <v>109</v>
+      </c>
+      <c r="D52" t="s">
+        <v>156</v>
+      </c>
+      <c r="E52" t="s">
+        <v>157</v>
+      </c>
+      <c r="F52" t="s">
+        <v>158</v>
+      </c>
+      <c r="G52" t="s">
+        <v>159</v>
+      </c>
+      <c r="H52" t="s">
+        <v>155</v>
+      </c>
+      <c r="I52">
+        <v>2</v>
+      </c>
+      <c r="M52" t="s">
+        <v>41</v>
+      </c>
+      <c r="P52" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q52">
+        <v>10</v>
+      </c>
+      <c r="R52" s="1">
+        <v>46133</v>
+      </c>
+      <c r="S52" s="1">
+        <v>46142</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:U50" xr:uid="{A0C223FD-F271-4B4C-83E7-B00E61ACB151}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/input.xlsx
+++ b/input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\prjectPlannerApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{727A093E-6D93-4EE2-8C7A-29C3F8B1ACE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F1CE14E-6207-49FE-BA13-FA0A19A7096D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E25E9825-3837-433F-B906-F8A5D1A19F77}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$U$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$U$53</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="170">
   <si>
     <t xml:space="preserve">PI_ID </t>
   </si>
@@ -170,9 +170,6 @@
     <t>Completed</t>
   </si>
   <si>
-    <t>Inprogress</t>
-  </si>
-  <si>
     <t>Spill over</t>
   </si>
   <si>
@@ -500,9 +497,6 @@
     <t>S42</t>
   </si>
   <si>
-    <t>Prescription Functionality as Web App</t>
-  </si>
-  <si>
     <t>Auto Suggestion of medicine and Test List, Medicine Time and Frequency</t>
   </si>
   <si>
@@ -519,6 +513,42 @@
   </si>
   <si>
     <t>S43</t>
+  </si>
+  <si>
+    <t>Career Page</t>
+  </si>
+  <si>
+    <t>F18</t>
+  </si>
+  <si>
+    <t>S44</t>
+  </si>
+  <si>
+    <t>Career</t>
+  </si>
+  <si>
+    <t>A Person can apply for a job from the Career Page</t>
+  </si>
+  <si>
+    <t>Prescription Functionality like Web App</t>
+  </si>
+  <si>
+    <t>In Progress</t>
+  </si>
+  <si>
+    <t>S45</t>
+  </si>
+  <si>
+    <t>The CLiniQ</t>
+  </si>
+  <si>
+    <t>F19</t>
+  </si>
+  <si>
+    <t>Play Store</t>
+  </si>
+  <si>
+    <t>DUNS Registration</t>
   </si>
 </sst>
 </file>
@@ -897,7 +927,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0C223FD-F271-4B4C-83E7-B00E61ACB151}">
-  <dimension ref="A1:U52"/>
+  <dimension ref="A1:U54"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.33203125" bestFit="1" customWidth="1"/>
@@ -979,10 +1009,10 @@
         <v>22</v>
       </c>
       <c r="T1" t="s">
+        <v>43</v>
+      </c>
+      <c r="U1" t="s">
         <v>44</v>
-      </c>
-      <c r="U1" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.3">
@@ -990,13 +1020,13 @@
         <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C2" t="s">
         <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E2" t="s">
         <v>17</v>
@@ -1034,13 +1064,13 @@
         <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C3" t="s">
         <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E3" t="s">
         <v>17</v>
@@ -1078,13 +1108,13 @@
         <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C4" t="s">
         <v>23</v>
       </c>
       <c r="D4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E4" t="s">
         <v>17</v>
@@ -1122,13 +1152,13 @@
         <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C5" t="s">
         <v>23</v>
       </c>
       <c r="D5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E5" t="s">
         <v>17</v>
@@ -1166,13 +1196,13 @@
         <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C6" t="s">
         <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E6" t="s">
         <v>17</v>
@@ -1210,13 +1240,13 @@
         <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C7" t="s">
         <v>23</v>
       </c>
       <c r="D7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E7" t="s">
         <v>17</v>
@@ -1254,13 +1284,13 @@
         <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C8" t="s">
         <v>23</v>
       </c>
       <c r="D8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E8" t="s">
         <v>17</v>
@@ -1298,13 +1328,13 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C9" t="s">
         <v>23</v>
       </c>
       <c r="D9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E9" t="s">
         <v>17</v>
@@ -1342,13 +1372,13 @@
         <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C10" t="s">
         <v>23</v>
       </c>
       <c r="D10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E10" t="s">
         <v>17</v>
@@ -1386,13 +1416,13 @@
         <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C11" t="s">
         <v>23</v>
       </c>
       <c r="D11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E11" t="s">
         <v>17</v>
@@ -1430,13 +1460,13 @@
         <v>16</v>
       </c>
       <c r="B12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C12" t="s">
         <v>23</v>
       </c>
       <c r="D12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E12" t="s">
         <v>17</v>
@@ -1474,13 +1504,13 @@
         <v>16</v>
       </c>
       <c r="B13" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C13" t="s">
         <v>23</v>
       </c>
       <c r="D13" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E13" t="s">
         <v>17</v>
@@ -1518,13 +1548,13 @@
         <v>16</v>
       </c>
       <c r="B14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C14" t="s">
         <v>23</v>
       </c>
       <c r="D14" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E14" t="s">
         <v>17</v>
@@ -1545,7 +1575,7 @@
         <v>41</v>
       </c>
       <c r="P14" t="s">
-        <v>43</v>
+        <v>164</v>
       </c>
       <c r="Q14">
         <v>10</v>
@@ -1562,25 +1592,25 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E15" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F15" t="s">
+        <v>45</v>
+      </c>
+      <c r="G15" t="s">
+        <v>65</v>
+      </c>
+      <c r="H15" t="s">
         <v>46</v>
-      </c>
-      <c r="G15" t="s">
-        <v>66</v>
-      </c>
-      <c r="H15" t="s">
-        <v>47</v>
       </c>
       <c r="I15">
         <v>2</v>
@@ -1606,25 +1636,25 @@
         <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C16" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D16" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E16" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F16" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I16">
         <v>2</v>
@@ -1650,25 +1680,25 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C17" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F17" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I17">
         <v>2</v>
@@ -1677,7 +1707,7 @@
         <v>41</v>
       </c>
       <c r="P17" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q17">
         <v>10</v>
@@ -1694,25 +1724,25 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C18" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D18" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E18" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F18" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G18" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H18" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I18">
         <v>2</v>
@@ -1738,25 +1768,25 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C19" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D19" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F19" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H19" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I19">
         <v>2</v>
@@ -1782,25 +1812,25 @@
         <v>16</v>
       </c>
       <c r="B20" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C20" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D20" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E20" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F20" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G20" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H20" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I20">
         <v>2</v>
@@ -1826,25 +1856,25 @@
         <v>16</v>
       </c>
       <c r="B21" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C21" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D21" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F21" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G21" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H21" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I21">
         <v>2</v>
@@ -1870,25 +1900,25 @@
         <v>16</v>
       </c>
       <c r="B22" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C22" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D22" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E22" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F22" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G22" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H22" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I22">
         <v>2</v>
@@ -1914,25 +1944,25 @@
         <v>16</v>
       </c>
       <c r="B23" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C23" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D23" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E23" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F23" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G23" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H23" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I23">
         <v>2</v>
@@ -1958,25 +1988,25 @@
         <v>16</v>
       </c>
       <c r="B24" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C24" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D24" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E24" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F24" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G24" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H24" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I24">
         <v>2</v>
@@ -2002,25 +2032,25 @@
         <v>16</v>
       </c>
       <c r="B25" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D25" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E25" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F25" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G25" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H25" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I25">
         <v>2</v>
@@ -2029,7 +2059,7 @@
         <v>41</v>
       </c>
       <c r="P25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q25">
         <v>10</v>
@@ -2046,25 +2076,25 @@
         <v>16</v>
       </c>
       <c r="B26" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C26" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D26" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E26" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F26" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G26" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H26" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I26">
         <v>2</v>
@@ -2090,25 +2120,25 @@
         <v>16</v>
       </c>
       <c r="B27" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C27" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D27" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E27" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F27" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G27" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H27" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I27">
         <v>2</v>
@@ -2134,25 +2164,25 @@
         <v>16</v>
       </c>
       <c r="B28" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C28" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D28" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E28" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F28" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G28" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H28" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I28">
         <v>2</v>
@@ -2178,25 +2208,25 @@
         <v>16</v>
       </c>
       <c r="B29" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C29" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D29" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E29" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F29" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G29" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H29" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I29">
         <v>2</v>
@@ -2222,25 +2252,25 @@
         <v>16</v>
       </c>
       <c r="B30" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C30" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D30" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E30" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F30" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G30" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H30" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I30">
         <v>2</v>
@@ -2266,25 +2296,25 @@
         <v>16</v>
       </c>
       <c r="B31" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C31" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E31" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F31" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G31" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H31" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I31">
         <v>2</v>
@@ -2310,25 +2340,25 @@
         <v>16</v>
       </c>
       <c r="B32" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C32" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D32" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E32" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F32" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G32" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H32" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I32">
         <v>2</v>
@@ -2354,25 +2384,25 @@
         <v>16</v>
       </c>
       <c r="B33" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C33" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D33" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E33" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F33" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G33" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H33" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I33">
         <v>2</v>
@@ -2398,25 +2428,25 @@
         <v>16</v>
       </c>
       <c r="B34" t="s">
+        <v>99</v>
+      </c>
+      <c r="C34" t="s">
+        <v>108</v>
+      </c>
+      <c r="D34" t="s">
+        <v>87</v>
+      </c>
+      <c r="E34" t="s">
+        <v>90</v>
+      </c>
+      <c r="F34" t="s">
+        <v>105</v>
+      </c>
+      <c r="G34" t="s">
+        <v>84</v>
+      </c>
+      <c r="H34" t="s">
         <v>100</v>
-      </c>
-      <c r="C34" t="s">
-        <v>109</v>
-      </c>
-      <c r="D34" t="s">
-        <v>88</v>
-      </c>
-      <c r="E34" t="s">
-        <v>91</v>
-      </c>
-      <c r="F34" t="s">
-        <v>106</v>
-      </c>
-      <c r="G34" t="s">
-        <v>85</v>
-      </c>
-      <c r="H34" t="s">
-        <v>101</v>
       </c>
       <c r="I34">
         <v>1</v>
@@ -2442,25 +2472,25 @@
         <v>16</v>
       </c>
       <c r="B35" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C35" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D35" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F35" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G35" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H35" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I35">
         <v>3</v>
@@ -2469,7 +2499,7 @@
         <v>41</v>
       </c>
       <c r="P35" t="s">
-        <v>43</v>
+        <v>164</v>
       </c>
       <c r="Q35">
         <v>10</v>
@@ -2486,25 +2516,25 @@
         <v>16</v>
       </c>
       <c r="B36" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C36" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D36" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E36" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F36" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G36" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H36" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I36">
         <v>3</v>
@@ -2513,7 +2543,7 @@
         <v>41</v>
       </c>
       <c r="P36" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q36">
         <v>10</v>
@@ -2530,25 +2560,25 @@
         <v>16</v>
       </c>
       <c r="B37" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C37" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D37" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E37" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F37" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G37" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H37" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I37">
         <v>1</v>
@@ -2574,25 +2604,25 @@
         <v>16</v>
       </c>
       <c r="B38" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C38" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D38" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E38" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F38" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G38" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H38" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I38">
         <v>3</v>
@@ -2601,7 +2631,7 @@
         <v>41</v>
       </c>
       <c r="P38" t="s">
-        <v>43</v>
+        <v>164</v>
       </c>
       <c r="Q38">
         <v>10</v>
@@ -2618,25 +2648,25 @@
         <v>16</v>
       </c>
       <c r="B39" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C39" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D39" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E39" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F39" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G39" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H39" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I39">
         <v>5</v>
@@ -2645,7 +2675,7 @@
         <v>41</v>
       </c>
       <c r="P39" t="s">
-        <v>99</v>
+        <v>164</v>
       </c>
       <c r="Q39">
         <v>10</v>
@@ -2662,25 +2692,25 @@
         <v>16</v>
       </c>
       <c r="B40" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C40" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D40" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E40" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F40" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G40" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I40">
         <v>5</v>
@@ -2689,7 +2719,7 @@
         <v>41</v>
       </c>
       <c r="P40" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q40">
         <v>10</v>
@@ -2706,34 +2736,34 @@
         <v>16</v>
       </c>
       <c r="B41" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C41" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D41" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E41" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F41" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G41" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H41" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I41">
         <v>5</v>
       </c>
       <c r="M41" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="P41" t="s">
-        <v>43</v>
+        <v>164</v>
       </c>
       <c r="Q41">
         <v>10</v>
@@ -2750,34 +2780,34 @@
         <v>16</v>
       </c>
       <c r="B42" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C42" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D42" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E42" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F42" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G42" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H42" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I42">
         <v>5</v>
       </c>
       <c r="M42" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q42">
         <v>10</v>
@@ -2794,25 +2824,25 @@
         <v>16</v>
       </c>
       <c r="B43" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C43" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D43" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E43" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F43" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G43" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H43" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I43">
         <v>5</v>
@@ -2821,7 +2851,7 @@
         <v>41</v>
       </c>
       <c r="P43" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q43">
         <v>10</v>
@@ -2838,26 +2868,26 @@
         <v>16</v>
       </c>
       <c r="B44" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C44" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D44" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E44" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F44" t="s">
+        <v>111</v>
+      </c>
+      <c r="G44" t="s">
+        <v>129</v>
+      </c>
+      <c r="H44" t="s">
         <v>112</v>
       </c>
-      <c r="G44" t="s">
-        <v>130</v>
-      </c>
-      <c r="H44" t="s">
-        <v>113</v>
-      </c>
       <c r="I44">
         <v>2</v>
       </c>
@@ -2865,7 +2895,7 @@
         <v>41</v>
       </c>
       <c r="P44" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q44">
         <v>10</v>
@@ -2882,34 +2912,34 @@
         <v>16</v>
       </c>
       <c r="B45" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C45" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D45" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E45" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F45" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G45" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H45" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I45">
         <v>5</v>
       </c>
       <c r="M45" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="P45" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q45">
         <v>10</v>
@@ -2926,34 +2956,34 @@
         <v>16</v>
       </c>
       <c r="B46" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C46" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D46" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E46" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F46" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G46" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H46" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I46">
         <v>5</v>
       </c>
       <c r="M46" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="P46" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q46">
         <v>10</v>
@@ -2967,28 +2997,28 @@
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B47" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C47" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D47" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E47" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F47" t="s">
         <v>24</v>
       </c>
       <c r="G47" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H47" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I47">
         <v>2</v>
@@ -2997,7 +3027,7 @@
         <v>41</v>
       </c>
       <c r="P47" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q47">
         <v>10</v>
@@ -3011,28 +3041,28 @@
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B48" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C48" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D48" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E48" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F48" t="s">
         <v>24</v>
       </c>
       <c r="G48" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H48" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I48">
         <v>2</v>
@@ -3041,7 +3071,7 @@
         <v>41</v>
       </c>
       <c r="P48" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q48">
         <v>10</v>
@@ -3055,28 +3085,28 @@
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B49" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C49" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D49" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E49" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F49" t="s">
         <v>24</v>
       </c>
       <c r="G49" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H49" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I49">
         <v>2</v>
@@ -3085,7 +3115,7 @@
         <v>41</v>
       </c>
       <c r="P49" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q49">
         <v>10</v>
@@ -3099,28 +3129,28 @@
     </row>
     <row r="50" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B50" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C50" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D50" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E50" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F50" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G50" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H50" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I50">
         <v>2</v>
@@ -3129,7 +3159,7 @@
         <v>41</v>
       </c>
       <c r="P50" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q50">
         <v>10</v>
@@ -3143,40 +3173,40 @@
     </row>
     <row r="51" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B51" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C51" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D51" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E51" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F51" t="s">
         <v>24</v>
       </c>
       <c r="G51" t="s">
+        <v>151</v>
+      </c>
+      <c r="H51" t="s">
+        <v>163</v>
+      </c>
+      <c r="I51">
+        <v>2</v>
+      </c>
+      <c r="L51" t="s">
         <v>152</v>
       </c>
-      <c r="H51" t="s">
-        <v>153</v>
-      </c>
-      <c r="I51">
-        <v>2</v>
-      </c>
-      <c r="L51" t="s">
-        <v>154</v>
-      </c>
       <c r="M51" t="s">
         <v>41</v>
       </c>
       <c r="P51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q51">
         <v>10</v>
@@ -3190,28 +3220,28 @@
     </row>
     <row r="52" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B52" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C52" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D52" t="s">
+        <v>154</v>
+      </c>
+      <c r="E52" t="s">
+        <v>155</v>
+      </c>
+      <c r="F52" t="s">
         <v>156</v>
       </c>
-      <c r="E52" t="s">
+      <c r="G52" t="s">
         <v>157</v>
       </c>
-      <c r="F52" t="s">
-        <v>158</v>
-      </c>
-      <c r="G52" t="s">
-        <v>159</v>
-      </c>
       <c r="H52" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="I52">
         <v>2</v>
@@ -3220,7 +3250,7 @@
         <v>41</v>
       </c>
       <c r="P52" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q52">
         <v>10</v>
@@ -3232,8 +3262,107 @@
         <v>46142</v>
       </c>
     </row>
+    <row r="53" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>137</v>
+      </c>
+      <c r="B53" t="s">
+        <v>99</v>
+      </c>
+      <c r="C53" t="s">
+        <v>108</v>
+      </c>
+      <c r="D53" t="s">
+        <v>154</v>
+      </c>
+      <c r="E53" t="s">
+        <v>159</v>
+      </c>
+      <c r="F53" t="s">
+        <v>161</v>
+      </c>
+      <c r="G53" t="s">
+        <v>160</v>
+      </c>
+      <c r="H53" t="s">
+        <v>158</v>
+      </c>
+      <c r="I53">
+        <v>2</v>
+      </c>
+      <c r="L53" t="s">
+        <v>162</v>
+      </c>
+      <c r="M53" t="s">
+        <v>41</v>
+      </c>
+      <c r="N53" s="1">
+        <v>46135</v>
+      </c>
+      <c r="O53" s="1">
+        <v>46135</v>
+      </c>
+      <c r="P53" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q53">
+        <v>10</v>
+      </c>
+      <c r="R53" s="1">
+        <v>46133</v>
+      </c>
+      <c r="S53" s="1">
+        <v>46142</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>137</v>
+      </c>
+      <c r="B54" t="s">
+        <v>99</v>
+      </c>
+      <c r="C54" t="s">
+        <v>108</v>
+      </c>
+      <c r="D54" t="s">
+        <v>166</v>
+      </c>
+      <c r="E54" t="s">
+        <v>167</v>
+      </c>
+      <c r="F54" t="s">
+        <v>168</v>
+      </c>
+      <c r="G54" t="s">
+        <v>165</v>
+      </c>
+      <c r="H54" t="s">
+        <v>169</v>
+      </c>
+      <c r="I54">
+        <v>2</v>
+      </c>
+      <c r="M54" t="s">
+        <v>41</v>
+      </c>
+      <c r="N54" s="1">
+        <v>46133</v>
+      </c>
+      <c r="P54" t="s">
+        <v>164</v>
+      </c>
+      <c r="Q54">
+        <v>10</v>
+      </c>
+      <c r="R54" s="1">
+        <v>46133</v>
+      </c>
+      <c r="S54" s="1">
+        <v>46142</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:U50" xr:uid="{A0C223FD-F271-4B4C-83E7-B00E61ACB151}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
